--- a/AAII_Financials/Yearly/ADC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ADC_YR_FIN.xlsx
@@ -2582,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>799400</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
